--- a/data/trans_dic/IP1001-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen asma</t>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,43</t>
+          <t>0,6; 5,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,09</t>
+          <t>0,65; 5,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,96</t>
+          <t>1,32; 7,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,14</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,79</t>
+          <t>1,29; 7,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,53</t>
+          <t>0,0; 15,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,44</t>
+          <t>0,52; 3,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,29</t>
+          <t>1,38; 5,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 8,74</t>
+          <t>1,29; 8,43</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,8</t>
+          <t>1,88; 8,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 8,15</t>
+          <t>0,63; 6,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,95</t>
+          <t>0,77; 7,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,64; 6,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,1</t>
+          <t>1,07; 6,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,03</t>
+          <t>1,11; 10,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,35</t>
+          <t>1,65; 6,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,69</t>
+          <t>0,56; 4,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,39</t>
+          <t>0,53; 2,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,34</t>
+          <t>1,49; 7,33</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,58</t>
+          <t>0,79; 8,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,56</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 11,12</t>
+          <t>2,79; 11,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,79</t>
+          <t>1,73; 9,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,29</t>
+          <t>2,58; 8,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,54</t>
+          <t>1,48; 6,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,59</t>
+          <t>1,02; 4,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,85</t>
+          <t>1,63; 5,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,83</t>
+          <t>0,6; 3,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,04</t>
+          <t>0,92; 4,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,64</t>
+          <t>1,12; 4,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,76</t>
+          <t>1,81; 5,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,03</t>
+          <t>0,7; 3,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,88</t>
+          <t>2,27; 7,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,73</t>
+          <t>1,25; 3,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,89</t>
+          <t>2,09; 4,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,25</t>
+          <t>1,07; 3,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,01</t>
+          <t>1,88; 4,98</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,89</t>
+          <t>2,08; 9,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,8</t>
+          <t>0,89; 5,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,71</t>
+          <t>1,31; 7,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,0</t>
+          <t>1,02; 5,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,5</t>
+          <t>0,97; 6,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,31</t>
+          <t>1,32; 6,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,81</t>
+          <t>0,95; 5,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,14</t>
+          <t>2,02; 6,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,82</t>
+          <t>1,53; 5,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,58</t>
+          <t>1,87; 5,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,04</t>
+          <t>0,96; 4,01</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,82</t>
+          <t>1,01; 9,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,44</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 13,3</t>
+          <t>2,09; 13,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,22</t>
+          <t>0,43; 5,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,28</t>
+          <t>0,93; 5,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,02</t>
+          <t>1,33; 7,19</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,19</t>
+          <t>2,08; 4,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,95</t>
+          <t>1,17; 2,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,27</t>
+          <t>1,37; 3,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,43</t>
+          <t>1,34; 3,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,78</t>
+          <t>1,81; 3,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,61</t>
+          <t>1,65; 3,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,02</t>
+          <t>1,8; 3,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,31</t>
+          <t>2,49; 5,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,65</t>
+          <t>2,18; 3,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,93</t>
+          <t>1,55; 2,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,17</t>
+          <t>1,84; 3,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,99</t>
+          <t>2,19; 4,11</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2482</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3489</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8160</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>626; 5718</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>540; 4869</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1380; 7875</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3097</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4767</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1290; 7627</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 21095</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1056; 6885</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5560</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2531; 10056</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3125; 20358</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3846</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1202</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2448</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6771</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1645; 7758</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4203</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>592; 6552</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>661; 6089</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>611; 5854</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1212; 7056</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1063; 10213</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2860; 11532</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1066; 7579</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1161; 6501</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2843; 13944</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6183</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3395</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8212</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4718</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>533; 5645</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3401</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4454</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3902</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2775; 11628</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3696</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1303; 7470</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2616</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4295; 13381</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5015</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2031; 9286</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4568</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4330</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7003</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3995</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5214</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4840</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7471</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>8964</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9170</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>14474</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8236</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>14178</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2053; 9495</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3346; 12013</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1339; 8168</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1997; 10717</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2265; 9295</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4095; 13073</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1482; 8413</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>4964; 16399</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>5033; 14694</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>9039; 21356</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4628; 14319</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>8194; 21720</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4994</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5023</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1549</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3407</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4266</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4459</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8401</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8100</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9360</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2162; 9593</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1325; 8706</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1783; 10047</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5384</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1294; 7445</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1358; 9212</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1888; 9436</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1551; 9065</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4671; 14477</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4424; 15007</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5230; 15591</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2712; 11316</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4441</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2273</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4832</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5182</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>615; 5522</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2433</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3090</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4869</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3073</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1504; 9943</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>636; 7388</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4694</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1198; 7059</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1874; 10138</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>19299</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12718</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>14549</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>17926</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>17466</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>27160</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>37225</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>30184</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>33802</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>41255</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>13276; 26978</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7907; 20062</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9219; 22670</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8837; 21890</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>12397; 25347</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>11782; 25513</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>12752; 27044</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>18653; 41588</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>28798; 48649</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>21545; 40241</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>25389; 43624</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>30819; 57866</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1001-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Clase-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,48</t>
+          <t>0,67; 5,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,86</t>
+          <t>0,65; 5,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,54</t>
+          <t>1,4; 8,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,64</t>
+          <t>1,31; 8,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,41</t>
+          <t>0,0; 11,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,41</t>
+          <t>0,48; 3,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,5</t>
+          <t>1,34; 5,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 8,43</t>
+          <t>1,28; 8,62</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 8,88</t>
+          <t>1,84; 9,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,92</t>
+          <t>0,62; 7,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,08</t>
+          <t>0,78; 6,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,09</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,26</t>
+          <t>1,07; 5,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,69</t>
+          <t>1,6; 11,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,65</t>
+          <t>1,88; 6,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,01</t>
+          <t>0,62; 4,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,98</t>
+          <t>0,54; 3,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,33</t>
+          <t>1,48; 7,08</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,38</t>
+          <t>0,8; 8,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,52</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 11,71</t>
+          <t>2,77; 10,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,9</t>
+          <t>1,65; 10,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,03</t>
+          <t>2,51; 8,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,76</t>
+          <t>1,4; 6,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,73</t>
+          <t>0,74; 4,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,84</t>
+          <t>1,67; 6,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,65</t>
+          <t>0,62; 3,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,92</t>
+          <t>0,97; 5,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,6</t>
+          <t>1,09; 4,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,76</t>
+          <t>1,79; 5,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,99</t>
+          <t>0,76; 4,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,51</t>
+          <t>2,18; 7,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,65</t>
+          <t>1,29; 3,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,94</t>
+          <t>2,14; 5,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,3</t>
+          <t>0,96; 3,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,98</t>
+          <t>1,99; 5,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,21</t>
+          <t>2,34; 9,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,84</t>
+          <t>0,89; 5,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,38</t>
+          <t>1,19; 7,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,85</t>
+          <t>1,02; 5,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,56</t>
+          <t>1,32; 6,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,59</t>
+          <t>1,1; 5,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,57</t>
+          <t>1,0; 6,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,26</t>
+          <t>1,98; 5,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,18</t>
+          <t>1,42; 4,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,58</t>
+          <t>1,95; 5,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,01</t>
+          <t>0,89; 4,02</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,04</t>
+          <t>0,98; 9,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 13,81</t>
+          <t>2,36; 14,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,02</t>
+          <t>0,43; 4,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,48</t>
+          <t>0,97; 5,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,19</t>
+          <t>1,19; 7,59</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,22</t>
+          <t>2,06; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,98</t>
+          <t>1,15; 2,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,38</t>
+          <t>1,33; 3,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,33</t>
+          <t>1,3; 3,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,7</t>
+          <t>1,74; 3,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,57</t>
+          <t>1,59; 3,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,81</t>
+          <t>1,81; 3,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,55</t>
+          <t>2,44; 5,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,68</t>
+          <t>2,18; 3,71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,9</t>
+          <t>1,54; 2,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,16</t>
+          <t>1,84; 3,22</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,11</t>
+          <t>2,17; 3,96</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>626; 5718</t>
+          <t>697; 5960</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1937,52 +1937,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>540; 4869</t>
+          <t>539; 4826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1380; 7875</t>
+          <t>1462; 8579</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3097</t>
+          <t>0; 3709</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4767</t>
+          <t>0; 4751</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1290; 7627</t>
+          <t>1308; 8226</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 21095</t>
+          <t>0; 15998</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1056; 6885</t>
+          <t>976; 7037</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5560</t>
+          <t>0; 5569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2531; 10056</t>
+          <t>2447; 9990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3125; 20358</t>
+          <t>3078; 20808</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1645; 7758</t>
+          <t>1607; 7941</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4203</t>
+          <t>0; 4536</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,47 +2150,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>592; 6552</t>
+          <t>585; 7447</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>661; 6089</t>
+          <t>668; 5879</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>611; 5854</t>
+          <t>0; 5484</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1212; 7056</t>
+          <t>1202; 6745</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1063; 10213</t>
+          <t>1525; 11242</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2860; 11532</t>
+          <t>3255; 10943</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1066; 7579</t>
+          <t>1164; 7617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1161; 6501</t>
+          <t>1179; 6864</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2843; 13944</t>
+          <t>2817; 13478</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>533; 5645</t>
+          <t>539; 5432</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3401</t>
+          <t>0; 3447</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4454</t>
+          <t>0; 4338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3902</t>
+          <t>0; 4328</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2775; 11628</t>
+          <t>2752; 10791</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3696</t>
+          <t>0; 3799</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1303; 7470</t>
+          <t>1245; 7582</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2616</t>
+          <t>0; 2928</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4295; 13381</t>
+          <t>4193; 13776</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5015</t>
+          <t>0; 4394</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2031; 9286</t>
+          <t>1918; 8933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 4994</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2053; 9495</t>
+          <t>1486; 8579</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3346; 12013</t>
+          <t>3428; 12917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1339; 8168</t>
+          <t>1376; 8736</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1997; 10717</t>
+          <t>2115; 10974</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2265; 9295</t>
+          <t>2207; 9117</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4095; 13073</t>
+          <t>4059; 13261</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1482; 8413</t>
+          <t>1602; 8667</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4964; 16399</t>
+          <t>4769; 15682</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5033; 14694</t>
+          <t>5188; 14492</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9039; 21356</t>
+          <t>9241; 21756</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4628; 14319</t>
+          <t>4172; 13573</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8194; 21720</t>
+          <t>8685; 23070</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2162; 9593</t>
+          <t>2434; 9995</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1325; 8706</t>
+          <t>1323; 8318</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1783; 10047</t>
+          <t>1624; 10560</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5384</t>
+          <t>0; 5253</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1294; 7445</t>
+          <t>1297; 7559</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1358; 9212</t>
+          <t>1851; 9064</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1888; 9436</t>
+          <t>1573; 8538</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1551; 9065</t>
+          <t>1625; 10143</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4671; 14477</t>
+          <t>4593; 13760</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4424; 15007</t>
+          <t>4107; 14080</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5230; 15591</t>
+          <t>5453; 16124</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2712; 11316</t>
+          <t>2504; 11339</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5182</t>
+          <t>0; 5615</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>615; 5522</t>
+          <t>598; 5530</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2433</t>
+          <t>0; 2229</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3090</t>
+          <t>0; 3631</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4869</t>
+          <t>0; 4720</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3073</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1504; 9943</t>
+          <t>1700; 10320</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>636; 7388</t>
+          <t>630; 6615</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4694</t>
+          <t>0; 4703</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1198; 7059</t>
+          <t>1247; 7340</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1874; 10138</t>
+          <t>1679; 10692</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13276; 26978</t>
+          <t>13131; 27854</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7907; 20062</t>
+          <t>7731; 19717</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9219; 22670</t>
+          <t>8906; 21508</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8837; 21890</t>
+          <t>8573; 22359</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12397; 25347</t>
+          <t>11936; 26008</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11782; 25513</t>
+          <t>11362; 25454</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12752; 27044</t>
+          <t>12845; 26863</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18653; 41588</t>
+          <t>18266; 41044</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28798; 48649</t>
+          <t>28851; 49164</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21545; 40241</t>
+          <t>21326; 38455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25389; 43624</t>
+          <t>25472; 44458</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30819; 57866</t>
+          <t>30456; 55653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1001-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,71</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,14</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1,3; 7,79</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,59</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,66; 5,43</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,65; 5,81</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 8,21</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,8</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,29</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,24</t>
+          <t>0,65; 6,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,69</t>
+          <t>1,53; 8,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,49</t>
+          <t>0,57; 3,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,46</t>
+          <t>1,13; 5,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 8,62</t>
+          <t>1,07; 5,26</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,09</t>
+          <t>0,78; 6,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>1,05; 6,1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1,06; 11,05</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,94; 9,8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 7,87</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,78; 6,84</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,71</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,07; 5,98</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 11,76</t>
+          <t>0,65; 8,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,31</t>
+          <t>1,69; 6,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,03</t>
+          <t>0,55; 3,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,14</t>
+          <t>0,55; 3,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,08</t>
+          <t>1,77; 7,63</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3,01%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,14%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,06</t>
+          <t>2,96; 11,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>1,74; 9,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,86</t>
+          <t>0,79; 8,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 4,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 10,05</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 8,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,26</t>
+          <t>2,56; 8,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,51</t>
+          <t>1,39; 6,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,27</t>
+          <t>1,15; 4,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,28</t>
+          <t>1,76; 5,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,91</t>
+          <t>0,74; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,03</t>
+          <t>2,26; 7,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,51</t>
+          <t>0,98; 4,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,85</t>
+          <t>1,68; 5,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,11</t>
+          <t>0,63; 3,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,18</t>
+          <t>1,3; 6,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,6</t>
+          <t>1,3; 3,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,03</t>
+          <t>2,07; 4,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,12</t>
+          <t>1,06; 3,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,29</t>
+          <t>2,2; 5,58</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,6</t>
+          <t>1,09; 6,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,58</t>
+          <t>0,93; 6,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,75</t>
+          <t>1,08; 6,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>1,16; 6,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,94</t>
+          <t>2,28; 8,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,45</t>
+          <t>0,99; 5,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,97</t>
+          <t>1,35; 7,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,24</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,95</t>
+          <t>2,07; 6,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,86</t>
+          <t>1,39; 4,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,77</t>
+          <t>1,78; 5,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,02</t>
+          <t>0,99; 4,2</t>
         </is>
       </c>
     </row>
@@ -1349,54 +1349,54 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,16%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3,96%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2,44%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,44</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,87</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1,88; 11,79</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,68</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,98; 9,05</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,24</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,02</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,38</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>1,01; 9,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,36; 14,33</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,49</t>
+          <t>0,43; 5,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,69</t>
+          <t>0,91; 5,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,59</t>
+          <t>1,18; 6,52</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,17%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,36</t>
+          <t>1,83; 3,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,92</t>
+          <t>1,62; 3,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,2</t>
+          <t>1,8; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,4</t>
+          <t>2,23; 4,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,8</t>
+          <t>2,08; 4,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,56</t>
+          <t>1,2; 2,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,78</t>
+          <t>1,37; 3,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,48</t>
+          <t>1,5; 3,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,71</t>
+          <t>2,17; 3,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,77</t>
+          <t>1,6; 2,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,22</t>
+          <t>1,81; 3,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,96</t>
+          <t>2,19; 3,91</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,54 +1859,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3489</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2482</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1787</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>1571</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3489</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>4450</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3097</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1571</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>5276</t>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>5869</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>697; 5960</t>
+          <t>0; 3708</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 5508</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1295; 7777</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6851</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>686; 5665</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>539; 4826</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1462; 8579</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3709</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4751</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1308; 8226</t>
+          <t>539; 5058</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 15998</t>
+          <t>1572; 8798</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>976; 7037</t>
+          <t>1151; 6937</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5569</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2447; 9990</t>
+          <t>2071; 9671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3078; 20808</t>
+          <t>2423; 11860</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,62 +2067,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4403</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3846</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1202</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2448</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2228</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6073</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>3066</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4324</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6073</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3066</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7020</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1607; 7941</t>
+          <t>666; 5974</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4536</t>
+          <t>0; 5611</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>1183; 6879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>971; 10102</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1693; 8566</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4447</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>585; 7447</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>668; 5879</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 5484</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1202; 6745</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1525; 11242</t>
+          <t>623; 8295</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3255; 10943</t>
+          <t>2923; 11017</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1164; 7617</t>
+          <t>1048; 6976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1179; 6864</t>
+          <t>1209; 7401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2817; 13478</t>
+          <t>3326; 14339</t>
         </is>
       </c>
     </row>
@@ -2207,37 +2207,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6183</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3395</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1323</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6183</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3395</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>816</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1340</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>539; 5432</t>
+          <t>2938; 11045</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3447</t>
+          <t>0; 3669</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4338</t>
+          <t>1314; 7388</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4328</t>
+          <t>0; 2757</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2752; 10791</t>
+          <t>532; 5781</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3799</t>
+          <t>0; 3844</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1245; 7582</t>
+          <t>0; 4290</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2928</t>
+          <t>0; 4409</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4193; 13776</t>
+          <t>4264; 13829</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4394</t>
+          <t>0; 4903</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1918; 8933</t>
+          <t>1913; 8977</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4994</t>
+          <t>0; 4673</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4840</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7471</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8686</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4330</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7003</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3995</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5214</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4840</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7471</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>13979</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1486; 8579</t>
+          <t>2329; 9373</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3428; 12917</t>
+          <t>3989; 13076</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1376; 8736</t>
+          <t>1558; 8503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2115; 10974</t>
+          <t>4571; 14641</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2207; 9117</t>
+          <t>1974; 9219</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4059; 13261</t>
+          <t>3461; 12029</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1602; 8667</t>
+          <t>1416; 8560</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4769; 15682</t>
+          <t>2329; 10925</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5188; 14492</t>
+          <t>5238; 15043</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9241; 21756</t>
+          <t>8970; 21150</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4172; 13573</t>
+          <t>4601; 14130</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8685; 23070</t>
+          <t>8377; 21235</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3407</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4266</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4336</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>4994</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3834</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>5023</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1549</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3407</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4266</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4336</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5867</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2434; 9995</t>
+          <t>1383; 7636</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1323; 8318</t>
+          <t>1305; 9134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1624; 10560</t>
+          <t>1539; 9027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5253</t>
+          <t>1721; 9217</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1297; 7559</t>
+          <t>2373; 9261</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1851; 9064</t>
+          <t>1472; 8654</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1573; 8538</t>
+          <t>1836; 10504</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1625; 10143</t>
+          <t>0; 5263</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4593; 13760</t>
+          <t>4798; 14217</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4107; 14080</t>
+          <t>4035; 13962</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5453; 16124</t>
+          <t>4983; 15597</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2504; 11339</t>
+          <t>2643; 11219</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,54 +2899,54 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3752</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1619</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2421</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2273</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>1369</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4441</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2273</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1369</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>3146</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4092</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5615</t>
+          <t>0; 3714</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>0; 4771</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3982</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1284; 8052</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5752</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>598; 5530</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2229</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3631</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4720</t>
-        </is>
-      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3656</t>
+          <t>615; 6002</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1700; 10320</t>
+          <t>0; 1566</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>630; 6615</t>
+          <t>635; 7686</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4703</t>
+          <t>0; 4572</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1247; 7340</t>
+          <t>1167; 6813</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1679; 10692</t>
+          <t>1640; 9046</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>17926</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17466</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>19299</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>12718</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>14549</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>17926</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>17466</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>38166</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13131; 27854</t>
+          <t>12531; 25899</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7731; 19717</t>
+          <t>11580; 25754</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8906; 21508</t>
+          <t>12771; 28552</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8573; 22359</t>
+          <t>15354; 33160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11936; 26008</t>
+          <t>13300; 26741</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11362; 25454</t>
+          <t>8065; 19864</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12845; 26863</t>
+          <t>9176; 21972</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>18266; 41044</t>
+          <t>9312; 23001</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28851; 49164</t>
+          <t>28662; 48342</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21326; 38455</t>
+          <t>22231; 40651</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25472; 44458</t>
+          <t>24933; 43743</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30456; 55653</t>
+          <t>28707; 51283</t>
         </is>
       </c>
     </row>
